--- a/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bernard est dans la salle de bain. Son nez chatouille. L'eau goutte un peu. Papa ouvre le tiroir. Papa tend un mouchoir. Bernard prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez se libère. Bernard va jeter le mouchoir. Il le met dans la poubelle. La poubelle fait un petit bruit. Papa dit : mouchoir, puis poubelle. Bernard se lave les mains. L'eau est tiède. Le savon sent la pomme. Bernard essuie. Il respire mieux. Papa lui caresse l'épaule. Bernard dit : le mouchoir est dans la poubelle.</t>
+          <t>Bernard est dans la salle de bain. Son nez chatouille. L'eau goutte un peu. Papa ouvre le tiroir. Papa tend un mouchoir. Bernard prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez se libère. Bernard va jeter le mouchoir. Il le met dans la poubelle. La poubelle fait un petit bruit. Mouchoir, puis poubelle. Bernard se lave les mains. L'eau est tiède. Le savon sent la pomme. Bernard essuie. Il respire mieux. Papa lui caresse l'épaule. Le mouchoir est dans la poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Bernard est dans la salle de bain. Son nez chatouille. L'eau goutte un peu. Papa ouvre le tiroir. Papa tend un mouchoir. Bernard prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez se libère. Bernard va jeter le mouchoir. Il le met dans la poubelle. La poubelle fait un petit bruit.
+papa|Mouchoir, puis poubelle.
+narrateur|Bernard se lave les mains. L'eau est tiède. Le savon sent la pomme. Bernard essuie. Il respire mieux. Papa lui caresse l'épaule.
+enfant-m|Le mouchoir est dans la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Bernard se mouche. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Bernard a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Bernard s'essuie les mains. Papa lui sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 enfant-m|Le mouchoir est dans la poubelle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Bernard se mouche. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Bernard a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Bernard s'essuie les mains. Papa lui sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le mouchoir de Bernard</t>
+          <t>Le canard et le tiroir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.HYG.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le canard du bain regarde le robinet. Une goutte. Deux gouttes. Le nez de Chouchou chatouille. Papa ouvre le tiroir. Mouchoir, puis poubelle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bernard est dans la salle de bain. Son nez chatouille. L'eau goutte un peu. Papa ouvre le tiroir. Papa tend un mouchoir. Bernard prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez se libère. Bernard va jeter le mouchoir. Il le met dans la poubelle. La poubelle fait un petit bruit. Mouchoir, puis poubelle. Bernard se lave les mains. L'eau est tiède. Le savon sent la pomme. Bernard essuie. Il respire mieux. Papa lui caresse l'épaule. Le mouchoir est dans la poubelle.</t>
+          <t>Le petit canard regarde le robinet. Une goutte. Deux gouttes. Les carreaux sont encore un peu humides. Le miroir a un nuage de buée. La serviette sent le coton chaud. Les pieds de Chouchou touchent le tapis doux. En ce moment, son nez chatouille. Ça coule un peu. Papa. Ça chatouille. J'ouvre le tiroir. Papa ouvre le tiroir. Le tiroir fait un petit glissement. Papa tend un mouchoir. Il est blanc, tout plié. Chouchou prend le mouchoir. Il se mouche, tout doux. Atchoum. Le nez se libère. Bravo, Chouchou. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La petite poubelle est près du lavabo. Chouchou jette le mouchoir. La poubelle fait un petit bruit. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Chouchou se lave les mains. L'eau est tiède. Le savon sent la pomme. Il essuie. Il respire mieux. Tu as fini de te laver les mains ? Oui. Le canard regarde encore. Une goutte. Le mouchoir est dans la poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1329,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Bernard est dans la salle de bain. Son nez chatouille. L'eau goutte un peu. Papa ouvre le tiroir. Papa tend un mouchoir. Bernard prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez se libère. Bernard va jeter le mouchoir. Il le met dans la poubelle. La poubelle fait un petit bruit.
+          <t>narrateur|Le petit canard regarde le robinet.
+narrateur|Une goutte.
+narrateur|Deux gouttes.
+narrateur|Les carreaux sont encore un peu humides.
+narrateur|Le miroir a un nuage de buée.
+narrateur|La serviette sent le coton chaud.
+narrateur|Les pieds de Chouchou touchent le tapis doux.
+narrateur|En ce moment, son nez chatouille.
+narrateur|Ça coule un peu.
+enfant-m|Papa.
+enfant-m|Ça chatouille.
+papa|J'ouvre le tiroir.
+narrateur|Papa ouvre le tiroir.
+narrateur|Le tiroir fait un petit glissement.
+narrateur|Papa tend un mouchoir.
+narrateur|Il est blanc, tout plié.
+narrateur|Chouchou prend le mouchoir.
+narrateur|Il se mouche, tout doux.
+narrateur|Atchoum.
+narrateur|Le nez se libère.
+papa|Bravo, Chouchou.
+papa|Tu as pris le mouchoir.
+papa|On va à la poubelle ?
+enfant-m|Oui, papa.
+narrateur|La petite poubelle est près du lavabo.
+narrateur|Chouchou jette le mouchoir.
+narrateur|La poubelle fait un petit bruit.
 papa|Mouchoir, puis poubelle.
-narrateur|Bernard se lave les mains. L'eau est tiède. Le savon sent la pomme. Bernard essuie. Il respire mieux. Papa lui caresse l'épaule.
+enfant-m|Mouchoir, puis poubelle.
+papa|C'est du bon travail.
+narrateur|Chouchou se lave les mains.
+narrateur|L'eau est tiède.
+narrateur|Le savon sent la pomme.
+narrateur|Il essuie.
+narrateur|Il respire mieux.
+papa|Tu as fini de te laver les mains ?
+enfant-m|Oui.
+narrateur|Le canard regarde encore.
+narrateur|Une goutte.
 enfant-m|Le mouchoir est dans la poubelle.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>robinet,poubelle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Bernard se mouche. Que prend-il ?</t>
+          <t>Chouchou se mouche. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Bernard se mouche. Que prend-il ?</t>
+          <t>narrateur|Chouchou se mouche.
+narrateur|Que prend-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bernard a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+          <t>Chouchou a pris un mouchoir. Il s'est mouché, tout doux. Il a jeté le mouchoir à la poubelle. Bravo. Tu as fait du bon travail. Mouchoir, puis poubelle. Oui, papa. Dans la poubelle. Le savon sent encore la pomme. Chouchou sent ses mains. Elles sont propres. Tu as vu le nuage dans le miroir ? Oui. Il part tout doux. Papa essuie un peu le miroir. Un visage apparaît. C'est moi. Oui. C'est toi, Chouchou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1729,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Bernard a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+          <t>narrateur|Chouchou a pris un mouchoir.
+narrateur|Il s'est mouché, tout doux.
+narrateur|Il a jeté le mouchoir à la poubelle.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Mouchoir, puis poubelle.
+enfant-m|Oui, papa.
+enfant-m|Dans la poubelle.
+narrateur|Le savon sent encore la pomme.
+narrateur|Chouchou sent ses mains.
+narrateur|Elles sont propres.
+papa|Tu as vu le nuage dans le miroir ?
+enfant-m|Oui.
+enfant-m|Il part tout doux.
+narrateur|Papa essuie un peu le miroir.
+narrateur|Un visage apparaît.
+enfant-m|C'est moi.
+papa|Oui.
+papa|C'est toi, Chouchou.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bernard s'essuie les mains. Papa lui sourit.</t>
+          <t>Chouchou s'essuie encore un peu. La serviette est chaude. Papa ferme le tiroir. Le tiroir fait un petit clic. On va dans la chambre ? Oui. Le canard reste près du robinet. Une dernière goutte. Papa. Merci. Merci, Chouchou. Tes mains sont sèches. On y va. Ils sortent. Le tapis est doux sous les pieds. La salle de bain redevient calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1915,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Bernard s'essuie les mains. Papa lui sourit.</t>
+          <t>narrateur|Chouchou s'essuie encore un peu.
+narrateur|La serviette est chaude.
+narrateur|Papa ferme le tiroir.
+narrateur|Le tiroir fait un petit clic.
+papa|On va dans la chambre ?
+enfant-m|Oui.
+narrateur|Le canard reste près du robinet.
+narrateur|Une dernière goutte.
+enfant-m|Papa.
+enfant-m|Merci.
+papa|Merci, Chouchou.
+papa|Tes mains sont sèches.
+papa|On y va.
+narrateur|Ils sortent.
+narrateur|Le tapis est doux sous les pieds.
+narrateur|La salle de bain redevient calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1958,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. Le canard a regardé. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2098,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai pris un mouchoir.
+enfant-m|Puis la poubelle.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+papa|Le canard a regardé.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le petit canard regarde le robinet. Une goutte. Deux gouttes. Les carreaux sont encore un peu humides. Le miroir a un nuage de buée. La serviette sent le coton chaud. Les pieds de Chouchou touchent le tapis doux. En ce moment, son nez chatouille. Ça coule un peu. Papa. Ça chatouille. J'ouvre le tiroir. Papa ouvre le tiroir. Le tiroir fait un petit glissement. Papa tend un mouchoir. Il est blanc, tout plié. Chouchou prend le mouchoir. Il se mouche, tout doux. Atchoum. Le nez se libère. Bravo, Chouchou. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La petite poubelle est près du lavabo. Chouchou jette le mouchoir. La poubelle fait un petit bruit. Mouchoir, puis poubelle. Mouchoir, puis poubelle. C'est du bon travail. Chouchou se lave les mains. L'eau est tiède. Le savon sent la pomme. Il essuie. Il respire mieux. Tu as fini de te laver les mains ? Oui. Le canard regarde encore. Une goutte. Le mouchoir est dans la poubelle.</t>
+          <t>Le petit canard regarde le robinet. Son bec est orange. Une goutte. Deux gouttes. Les carreaux sont encore un peu humides. Ils sont blancs et bleus. Le miroir a un nuage de buée. La serviette sent le coton chaud. Le radiateur est tiède. Les pieds de Chouchou touchent le tapis doux. Le tapis est gris, tout pelucheux. En ce moment, son nez chatouille. Ça coule un peu. Papa. Ça chatouille. J'ouvre le tiroir. Papa ouvre le tiroir. Le tiroir fait un petit glissement. Il sent le bois. Tiens. Un mouchoir. Papa tend un mouchoir. Il est blanc, tout plié. Chouchou prend le mouchoir. Il se mouche, tout doux. Atchoum. Le nez se libère. Bravo, Chouchou. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La petite poubelle est près du lavabo. Elle a un couvercle blanc. Chouchou jette le mouchoir. La poubelle fait un petit bruit. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. Chouchou se lave les mains. L'eau est tiède. Le savon sent la pomme. Il essuie. Il respire mieux. Tu as fini de te laver les mains ? Oui. Le canard regarde encore. Une goutte. Le mouchoir est dans la poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bernard est dans la salle de bain. Son nez chatouille. L'eau goutte un peu. Papa ouvre le tiroir. Papa tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Bernard prend le mouchoir. Il se mouche tout doux. Atchoum. Le nez se libère. Bernard va jeter le mouchoir. Il le met dans la poubelle. La poubelle fait un petit bruit. Papa dit : mouchoir, puis poubelle. Bernard se lave les mains. L'eau est tiède. Le savon sent la pomme. Bernard essuie. Il respire mieux. Papa lui caresse l'épaule. Bernard dit : le mouchoir est dans la poubelle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit canard regarde le robinet. Son bec est orange. Une goutte. Deux gouttes. Les carreaux sont encore un peu humides. Ils sont blancs et bleus. Le miroir a un nuage de buée. La serviette sent le coton chaud. Le radiateur est tiède. Les pieds de Chouchou touchent le tapis doux. Le tapis est gris, tout pelucheux. En ce moment, son nez chatouille. Ça coule un peu. Papa. Ça chatouille. J'ouvre le tiroir. Papa ouvre le tiroir. Le tiroir fait un petit glissement. Il sent le bois. Tiens. Un mouchoir. Papa tend un mouchoir. Il est blanc, tout plié. Chouchou prend le mouchoir. Il se mouche, tout doux. Atchoum. Le nez se libère. Bravo, Chouchou. Tu as pris le mouchoir. On va à la poubelle ? Oui, papa. La petite poubelle est près du lavabo. Elle a un couvercle blanc. Chouchou jette le mouchoir. La poubelle fait un petit bruit. Mouchoir, puis poubelle. Mouchoir, puis poubelle. Tu as fini de jeter le mouchoir ? Oui. Chouchou se lave les mains. L'eau est tiède. Le savon sent la pomme. Il essuie. Il respire mieux. Tu as fini de te laver les mains ? Oui. Le canard regarde encore. Une goutte. Le mouchoir est dans la poubelle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1330,12 +1330,16 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Le petit canard regarde le robinet.
+narrateur|Son bec est orange.
 narrateur|Une goutte.
 narrateur|Deux gouttes.
 narrateur|Les carreaux sont encore un peu humides.
+narrateur|Ils sont blancs et bleus.
 narrateur|Le miroir a un nuage de buée.
 narrateur|La serviette sent le coton chaud.
+narrateur|Le radiateur est tiède.
 narrateur|Les pieds de Chouchou touchent le tapis doux.
+narrateur|Le tapis est gris, tout pelucheux.
 narrateur|En ce moment, son nez chatouille.
 narrateur|Ça coule un peu.
 enfant-m|Papa.
@@ -1343,6 +1347,9 @@
 papa|J'ouvre le tiroir.
 narrateur|Papa ouvre le tiroir.
 narrateur|Le tiroir fait un petit glissement.
+narrateur|Il sent le bois.
+papa|Tiens.
+papa|Un mouchoir.
 narrateur|Papa tend un mouchoir.
 narrateur|Il est blanc, tout plié.
 narrateur|Chouchou prend le mouchoir.
@@ -1354,11 +1361,13 @@
 papa|On va à la poubelle ?
 enfant-m|Oui, papa.
 narrateur|La petite poubelle est près du lavabo.
+narrateur|Elle a un couvercle blanc.
 narrateur|Chouchou jette le mouchoir.
 narrateur|La poubelle fait un petit bruit.
 papa|Mouchoir, puis poubelle.
 enfant-m|Mouchoir, puis poubelle.
-papa|C'est du bon travail.
+papa|Tu as fini de jeter le mouchoir ?
+enfant-m|Oui.
 narrateur|Chouchou se lave les mains.
 narrateur|L'eau est tiède.
 narrateur|Le savon sent la pomme.
@@ -1405,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Bernard se mouche. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou se mouche. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1560,7 +1569,6 @@
 narrateur|Que prend-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1585,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a pris un mouchoir. Il s'est mouché, tout doux. Il a jeté le mouchoir à la poubelle. Bravo. Tu as fait du bon travail. Mouchoir, puis poubelle. Oui, papa. Dans la poubelle. Le savon sent encore la pomme. Chouchou sent ses mains. Elles sont propres. Tu as vu le nuage dans le miroir ? Oui. Il part tout doux. Papa essuie un peu le miroir. Un visage apparaît. C'est moi. Oui. C'est toi, Chouchou.</t>
+          <t>Chouchou a pris un mouchoir. Il s'est mouché, tout doux. Il a jeté le mouchoir à la poubelle. Bravo. Mouchoir, puis poubelle. Oui, papa. Dans la poubelle. Le savon sent encore la pomme. Chouchou sent ses mains. Elles sont propres. Tu as vu le nuage dans le miroir ? Oui. Il part tout doux. Papa essuie un peu le miroir. Un visage apparaît. C'est moi. Oui. C'est toi, Chouchou.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bernard a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Il s'est mouché. Il a jeté le mouchoir à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a pris un mouchoir. Il s'est mouché, tout doux. Il a jeté le mouchoir à la poubelle. Bravo. Mouchoir, puis poubelle. Oui, papa. Dans la poubelle. Le savon sent encore la pomme. Chouchou sent ses mains. Elles sont propres. Tu as vu le nuage dans le miroir ? Oui. Il part tout doux. Papa essuie un peu le miroir. Un visage apparaît. C'est moi. Oui. C'est toi, Chouchou.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1733,7 +1741,6 @@
 narrateur|Il s'est mouché, tout doux.
 narrateur|Il a jeté le mouchoir à la poubelle.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 papa|Mouchoir, puis poubelle.
 enfant-m|Oui, papa.
 enfant-m|Dans la poubelle.
@@ -1750,7 +1757,6 @@
 papa|C'est toi, Chouchou.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1780,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Bernard s'essuie les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Papa lui sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou s'essuie encore un peu. La serviette est chaude. Papa ferme le tiroir. Le tiroir fait un petit clic. On va dans la chambre ? Oui. Le canard reste près du robinet. Une dernière goutte. Papa. Merci. Merci, Chouchou. Tes mains sont sèches. On y va. Ils sortent. Le tapis est doux sous les pieds. La salle de bain redevient calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1933,7 +1939,6 @@
 narrateur|La salle de bain redevient calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Tu as fait du bon travail. Le canard a regardé. L'histoire est finie.</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Le canard a regardé.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai pris un mouchoir. Puis la poubelle. Bravo. Le canard a regardé.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2101,12 +2106,9 @@
           <t>enfant-m|J'ai pris un mouchoir.
 enfant-m|Puis la poubelle.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-papa|Le canard a regardé.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Le canard a regardé.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-08.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bernard, papa</t>
+          <t>Chouchou, papa</t>
         </is>
       </c>
     </row>
